--- a/artfynd/S 3289-2022 artfynd.xlsx
+++ b/artfynd/S 3289-2022 artfynd.xlsx
@@ -2540,7 +2540,7 @@
         <v>136177268</v>
       </c>
       <c r="B18" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>136177271</v>
       </c>
       <c r="B19" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
